--- a/data/processed/harmonization/Major_and_trace_elements_total__Total_manganese/harmonized.xlsx
+++ b/data/processed/harmonization/Major_and_trace_elements_total__Total_manganese/harmonized.xlsx
@@ -432,7 +432,7 @@
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="58" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="49" customWidth="1" min="7" max="7"/>
@@ -3046,12 +3046,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>4:20-29</t>
+          <t>Hu:4:20-29</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3081,7 +3081,7 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3098,12 +3098,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>4:10-20</t>
+          <t>Hu:4:10-20</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3133,7 +3133,7 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3150,12 +3150,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>4:0-10</t>
+          <t>Hu:4:0-10</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3202,12 +3202,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>4:-10-0</t>
+          <t>Ho:4:-10-0</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3237,7 +3237,7 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3254,12 +3254,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>4:-20--10</t>
+          <t>Ho:4:-20--10</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3289,7 +3289,7 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3306,12 +3306,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>4:-30--20</t>
+          <t>Ho:4:-30--20</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3341,7 +3341,7 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>4:-40--30</t>
+          <t>Ho:4:-40--30</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3393,7 +3393,7 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3410,12 +3410,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>4:-50--40</t>
+          <t>Ho:4:-50--40</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3445,7 +3445,7 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3462,12 +3462,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>4:-60--50</t>
+          <t>Ho:4:-60--50</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3514,12 +3514,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>4:-70--60</t>
+          <t>Ho:4:-70--60</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3549,7 +3549,7 @@
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3566,12 +3566,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>4:-80--70</t>
+          <t>Ho:4:-80--70</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3618,12 +3618,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>4:-90--80</t>
+          <t>Ho:4:-90--80</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3653,7 +3653,7 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3670,12 +3670,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>4:-100--90</t>
+          <t>Ho:4:-100--90</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3705,7 +3705,7 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3722,12 +3722,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>4:-125--100</t>
+          <t>Ho:4:-125--100</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3757,7 +3757,7 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3774,12 +3774,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>4:-150--125</t>
+          <t>Ho:4:-150--125</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3809,7 +3809,7 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3826,12 +3826,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>4:-175--150</t>
+          <t>Ho:4:-175--150</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -3861,7 +3861,7 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3878,12 +3878,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>4:-200--175</t>
+          <t>Ho:4:-200--175</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -3913,7 +3913,7 @@
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3930,12 +3930,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>4:-250--200</t>
+          <t>Ho:4:-250--200</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3982,12 +3982,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>5:0-24</t>
+          <t>Hu:5:0-24</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -4017,7 +4017,7 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4034,12 +4034,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>5:10-18</t>
+          <t>Hu:5:10-18</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4086,12 +4086,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>5:0-10</t>
+          <t>Hu:5:0-10</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -4121,7 +4121,7 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4138,12 +4138,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>5:-10-0</t>
+          <t>Ho:5:-10-0</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -4173,7 +4173,7 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4190,12 +4190,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>5:-20--10</t>
+          <t>Ho:5:-20--10</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -4225,7 +4225,7 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4242,12 +4242,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>5:-30--20</t>
+          <t>Ho:5:-30--20</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -4277,7 +4277,7 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4294,12 +4294,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>5:-40--30</t>
+          <t>Ho:5:-40--30</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4329,7 +4329,7 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4346,12 +4346,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>5:-50--40</t>
+          <t>Ho:5:-50--40</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -4381,7 +4381,7 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>5:-60--50</t>
+          <t>Ho:5:-60--50</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -4433,7 +4433,7 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4450,12 +4450,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>5:-70--60</t>
+          <t>Ho:5:-70--60</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4502,12 +4502,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>5:-80--70</t>
+          <t>Ho:5:-80--70</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -4537,7 +4537,7 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4554,12 +4554,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>5:-90--80</t>
+          <t>Ho:5:-90--80</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -4589,7 +4589,7 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>5:-100--90</t>
+          <t>Ho:5:-100--90</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -4641,7 +4641,7 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4658,12 +4658,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>5:-125--100</t>
+          <t>Ho:5:-125--100</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -4693,7 +4693,7 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4710,12 +4710,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>5:-150--125</t>
+          <t>Ho:5:-150--125</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -4745,7 +4745,7 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4762,12 +4762,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>5:-175--150</t>
+          <t>Ho:5:-175--150</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4814,12 +4814,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>5:-200--175</t>
+          <t>Ho:5:-200--175</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -4849,7 +4849,7 @@
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4866,12 +4866,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>5:-250--200</t>
+          <t>Ho:5:-250--200</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4918,12 +4918,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>5:-300--250</t>
+          <t>Ho:5:-300--250</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -4953,7 +4953,7 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>6:20-30</t>
+          <t>Hu:6:20-30</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -5005,7 +5005,7 @@
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5022,12 +5022,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>6:10-20</t>
+          <t>Hu:6:10-20</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5074,12 +5074,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>6:0-10</t>
+          <t>Hu:6:0-10</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -5109,7 +5109,7 @@
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5126,12 +5126,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>6:10-20</t>
+          <t>Hu:6:10-20</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -5161,7 +5161,7 @@
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5178,12 +5178,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>6:0-10</t>
+          <t>Hu:6:0-10</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5230,12 +5230,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>6:-10-0</t>
+          <t>Ho:6:-10-0</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -5265,7 +5265,7 @@
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>6:-20--10</t>
+          <t>Ho:6:-20--10</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5334,12 +5334,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>6:-30--20</t>
+          <t>Ho:6:-30--20</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -5369,7 +5369,7 @@
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5386,12 +5386,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>6:-40--30</t>
+          <t>Ho:6:-40--30</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5438,12 +5438,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>6:-50--40</t>
+          <t>Ho:6:-50--40</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -5473,7 +5473,7 @@
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5490,12 +5490,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>6:-60--50</t>
+          <t>Ho:6:-60--50</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -5525,7 +5525,7 @@
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>6:-70--60</t>
+          <t>Ho:6:-70--60</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -5577,7 +5577,7 @@
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5594,12 +5594,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>6:-80--70</t>
+          <t>Ho:6:-80--70</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -5629,7 +5629,7 @@
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5646,12 +5646,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>6:-90--80</t>
+          <t>Ho:6:-90--80</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -5681,7 +5681,7 @@
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5698,12 +5698,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>6:-100--90</t>
+          <t>Ho:6:-100--90</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -5733,7 +5733,7 @@
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>6:-125--100</t>
+          <t>Ho:6:-125--100</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -5785,7 +5785,7 @@
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5802,12 +5802,12 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>6:-150--125</t>
+          <t>Ho:6:-150--125</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -5837,7 +5837,7 @@
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5854,12 +5854,12 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>6:-175--150</t>
+          <t>Ho:6:-175--150</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -5889,7 +5889,7 @@
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5906,12 +5906,12 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>6:-200--175</t>
+          <t>Ho:6:-200--175</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -5941,7 +5941,7 @@
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5958,12 +5958,12 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>6:-250--200</t>
+          <t>Ho:6:-250--200</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -5993,7 +5993,7 @@
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6010,12 +6010,12 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>7:0-10</t>
+          <t>Hu:7:0-10</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -6045,7 +6045,7 @@
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6062,12 +6062,12 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>7:20-22</t>
+          <t>Hu:7:20-22</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -6097,7 +6097,7 @@
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>7:10-20</t>
+          <t>Hu:7:10-20</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -6149,7 +6149,7 @@
       <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6166,12 +6166,12 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>7:0-10</t>
+          <t>Hu:7:0-10</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6218,12 +6218,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>7:-10-0</t>
+          <t>Ho:7:-10-0</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -6253,7 +6253,7 @@
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6270,12 +6270,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>7:-20--10</t>
+          <t>Ho:7:-20--10</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -6305,7 +6305,7 @@
       <c r="K116" s="2" t="inlineStr"/>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6322,12 +6322,12 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>7:-30--20</t>
+          <t>Ho:7:-30--20</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -6357,7 +6357,7 @@
       <c r="K117" s="2" t="inlineStr"/>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6374,12 +6374,12 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>7:-40--30</t>
+          <t>Ho:7:-40--30</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -6409,7 +6409,7 @@
       <c r="K118" s="2" t="inlineStr"/>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>7:-50--40</t>
+          <t>Ho:7:-50--40</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -6461,7 +6461,7 @@
       <c r="K119" s="2" t="inlineStr"/>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6478,12 +6478,12 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>7:-60--50</t>
+          <t>Ho:7:-60--50</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -6513,7 +6513,7 @@
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6530,12 +6530,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>7:-70--60</t>
+          <t>Ho:7:-70--60</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -6565,7 +6565,7 @@
       <c r="K121" s="2" t="inlineStr"/>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6582,12 +6582,12 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>7:-80--70</t>
+          <t>Ho:7:-80--70</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -6617,7 +6617,7 @@
       <c r="K122" s="2" t="inlineStr"/>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>7:-90--80</t>
+          <t>Ho:7:-90--80</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -6669,7 +6669,7 @@
       <c r="K123" s="2" t="inlineStr"/>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6686,12 +6686,12 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>7:-100--90</t>
+          <t>Ho:7:-100--90</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -6721,7 +6721,7 @@
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6738,12 +6738,12 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>7:-125--100</t>
+          <t>Ho:7:-125--100</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -6773,7 +6773,7 @@
       <c r="K125" s="2" t="inlineStr"/>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6790,12 +6790,12 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>7:-150--125</t>
+          <t>Ho:7:-150--125</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       <c r="K126" s="2" t="inlineStr"/>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6842,12 +6842,12 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>7:-175--150</t>
+          <t>Ho:7:-175--150</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -6877,7 +6877,7 @@
       <c r="K127" s="2" t="inlineStr"/>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>7:-200--175</t>
+          <t>Ho:7:-200--175</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -6929,7 +6929,7 @@
       <c r="K128" s="2" t="inlineStr"/>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6946,12 +6946,12 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>7:-250--200</t>
+          <t>Ho:7:-250--200</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -6981,7 +6981,7 @@
       <c r="K129" s="2" t="inlineStr"/>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>7:-300--250</t>
+          <t>Ho:7:-300--250</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -7033,7 +7033,7 @@
       <c r="K130" s="2" t="inlineStr"/>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7050,12 +7050,12 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>8:10-20</t>
+          <t>Hu:8:10-20</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -7085,7 +7085,7 @@
       <c r="K131" s="2" t="inlineStr"/>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>8:0-10</t>
+          <t>Hu:8:0-10</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -7137,7 +7137,7 @@
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7154,12 +7154,12 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>8:-10-0</t>
+          <t>Hu:8:-10-0</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -7189,7 +7189,7 @@
       <c r="K133" s="2" t="inlineStr"/>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7206,12 +7206,12 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>8:-10-0</t>
+          <t>Ho:8:-10-0</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -7241,7 +7241,7 @@
       <c r="K134" s="2" t="inlineStr"/>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7258,12 +7258,12 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>8:-20--10</t>
+          <t>Ho:8:-20--10</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -7293,7 +7293,7 @@
       <c r="K135" s="2" t="inlineStr"/>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7310,12 +7310,12 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>8:-30--20</t>
+          <t>Ho:8:-30--20</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -7345,7 +7345,7 @@
       <c r="K136" s="2" t="inlineStr"/>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7362,12 +7362,12 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>8:-40--30</t>
+          <t>Ho:8:-40--30</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       <c r="K137" s="2" t="inlineStr"/>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7414,12 +7414,12 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>8:-50--40</t>
+          <t>Ho:8:-50--40</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -7449,7 +7449,7 @@
       <c r="K138" s="2" t="inlineStr"/>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>8:-60--50</t>
+          <t>Ho:8:-60--50</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -7501,7 +7501,7 @@
       <c r="K139" s="2" t="inlineStr"/>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7518,12 +7518,12 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>8:-70--60</t>
+          <t>Ho:8:-70--60</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -7553,7 +7553,7 @@
       <c r="K140" s="2" t="inlineStr"/>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7570,12 +7570,12 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>8:-80--70</t>
+          <t>Ho:8:-80--70</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       <c r="K141" s="2" t="inlineStr"/>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7622,12 +7622,12 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>8:-90--80</t>
+          <t>Ho:8:-90--80</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -7657,7 +7657,7 @@
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7674,12 +7674,12 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>8:-100--90</t>
+          <t>Ho:8:-100--90</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -7709,7 +7709,7 @@
       <c r="K143" s="2" t="inlineStr"/>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7726,12 +7726,12 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>8:-125--100</t>
+          <t>Ho:8:-125--100</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -7761,7 +7761,7 @@
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7778,12 +7778,12 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>8:-150--125</t>
+          <t>Ho:8:-150--125</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -7813,7 +7813,7 @@
       <c r="K145" s="2" t="inlineStr"/>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>8:-175--150</t>
+          <t>Ho:8:-175--150</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -7865,7 +7865,7 @@
       <c r="K146" s="2" t="inlineStr"/>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7882,12 +7882,12 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>8:-200--175</t>
+          <t>Ho:8:-200--175</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -7917,7 +7917,7 @@
       <c r="K147" s="2" t="inlineStr"/>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7934,12 +7934,12 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>9:10-18</t>
+          <t>Hu:9:10-18</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -7969,7 +7969,7 @@
       <c r="K148" s="2" t="inlineStr"/>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7986,12 +7986,12 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>9:0-10</t>
+          <t>Hu:9:0-10</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -8021,7 +8021,7 @@
       <c r="K149" s="2" t="inlineStr"/>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8038,12 +8038,12 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>9:-10-0</t>
+          <t>Ho:9:-10-0</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -8073,7 +8073,7 @@
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8090,12 +8090,12 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>9:-20--10</t>
+          <t>Ho:9:-20--10</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -8125,7 +8125,7 @@
       <c r="K151" s="2" t="inlineStr"/>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8142,12 +8142,12 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>9:-30--20</t>
+          <t>Ho:9:-30--20</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -8177,7 +8177,7 @@
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8194,12 +8194,12 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>9:-40--30</t>
+          <t>Ho:9:-40--30</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -8229,7 +8229,7 @@
       <c r="K153" s="2" t="inlineStr"/>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8246,12 +8246,12 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>9:-50--40</t>
+          <t>Ho:9:-50--40</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -8281,7 +8281,7 @@
       <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8298,12 +8298,12 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>9:-60--50</t>
+          <t>Ho:9:-60--50</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -8333,7 +8333,7 @@
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8350,12 +8350,12 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>9:-70--60</t>
+          <t>Ho:9:-70--60</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -8385,7 +8385,7 @@
       <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8402,12 +8402,12 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>9:-80--70</t>
+          <t>Ho:9:-80--70</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -8437,7 +8437,7 @@
       <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8454,12 +8454,12 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>9:-90--80</t>
+          <t>Ho:9:-90--80</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -8489,7 +8489,7 @@
       <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8506,12 +8506,12 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>9:-100--90</t>
+          <t>Ho:9:-100--90</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -8541,7 +8541,7 @@
       <c r="K159" s="2" t="inlineStr"/>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8558,12 +8558,12 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>9:-125--100</t>
+          <t>Ho:9:-125--100</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -8593,7 +8593,7 @@
       <c r="K160" s="2" t="inlineStr"/>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>9:-150--125</t>
+          <t>Ho:9:-150--125</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -8645,7 +8645,7 @@
       <c r="K161" s="2" t="inlineStr"/>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8662,12 +8662,12 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>9:-175--150</t>
+          <t>Ho:9:-175--150</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -8697,7 +8697,7 @@
       <c r="K162" s="2" t="inlineStr"/>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8714,12 +8714,12 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>9:-200--175</t>
+          <t>Ho:9:-200--175</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -8749,7 +8749,7 @@
       <c r="K163" s="2" t="inlineStr"/>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8766,12 +8766,12 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>9:-250--200</t>
+          <t>Ho:9:-250--200</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -8801,7 +8801,7 @@
       <c r="K164" s="2" t="inlineStr"/>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8818,12 +8818,12 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>9:-300--250</t>
+          <t>Ho:9:-300--250</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -8853,7 +8853,7 @@
       <c r="K165" s="2" t="inlineStr"/>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8870,12 +8870,12 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>10:20-29</t>
+          <t>Hu:10:20-29</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -8905,7 +8905,7 @@
       <c r="K166" s="2" t="inlineStr"/>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>10:10-20</t>
+          <t>Hu:10:10-20</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -8957,7 +8957,7 @@
       <c r="K167" s="2" t="inlineStr"/>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8974,12 +8974,12 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>10:0-10</t>
+          <t>Hu:10:0-10</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -9009,7 +9009,7 @@
       <c r="K168" s="2" t="inlineStr"/>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9026,12 +9026,12 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>10:-10-0</t>
+          <t>Ho:10:-10-0</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -9061,7 +9061,7 @@
       <c r="K169" s="2" t="inlineStr"/>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9078,12 +9078,12 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>10:-20--10</t>
+          <t>Ho:10:-20--10</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -9113,7 +9113,7 @@
       <c r="K170" s="2" t="inlineStr"/>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9130,12 +9130,12 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>10:-30--20</t>
+          <t>Ho:10:-30--20</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -9165,7 +9165,7 @@
       <c r="K171" s="2" t="inlineStr"/>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9182,12 +9182,12 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>10:-40--30</t>
+          <t>Ho:10:-40--30</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -9217,7 +9217,7 @@
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>10:-50--40</t>
+          <t>Ho:10:-50--40</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -9269,7 +9269,7 @@
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>10:-60--50</t>
+          <t>Ho:10:-60--50</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -9321,7 +9321,7 @@
       <c r="K174" s="2" t="inlineStr"/>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9338,12 +9338,12 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>10:-70--60</t>
+          <t>Ho:10:-70--60</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -9373,7 +9373,7 @@
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9390,12 +9390,12 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>10:-80--70</t>
+          <t>Ho:10:-80--70</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -9425,7 +9425,7 @@
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9442,12 +9442,12 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>10:-90--80</t>
+          <t>Ho:10:-90--80</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -9477,7 +9477,7 @@
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>10:-100--90</t>
+          <t>Ho:10:-100--90</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -9529,7 +9529,7 @@
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9546,12 +9546,12 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>10:-125--100</t>
+          <t>Ho:10:-125--100</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -9581,7 +9581,7 @@
       <c r="K179" s="2" t="inlineStr"/>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9598,12 +9598,12 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>10:-150--125</t>
+          <t>Ho:10:-150--125</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -9633,7 +9633,7 @@
       <c r="K180" s="2" t="inlineStr"/>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9650,12 +9650,12 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>10:-175--150</t>
+          <t>Ho:10:-175--150</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -9685,7 +9685,7 @@
       <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9702,12 +9702,12 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>10:-200--175</t>
+          <t>Ho:10:-200--175</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -9737,7 +9737,7 @@
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9754,12 +9754,12 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>10:-225--200</t>
+          <t>Ho:10:-225--200</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -9789,7 +9789,7 @@
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9806,12 +9806,12 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>10:-255--225</t>
+          <t>Ho:10:-255--225</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -9841,7 +9841,7 @@
       <c r="K184" s="2" t="inlineStr"/>
       <c r="L184" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9858,12 +9858,12 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>10:-275--255</t>
+          <t>Ho:10:-275--255</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -9893,7 +9893,7 @@
       <c r="K185" s="2" t="inlineStr"/>
       <c r="L185" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9910,12 +9910,12 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>11:10-18</t>
+          <t>Hu:11:10-18</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -9945,7 +9945,7 @@
       <c r="K186" s="2" t="inlineStr"/>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9962,12 +9962,12 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>11:0-10</t>
+          <t>Hu:11:0-10</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -9997,7 +9997,7 @@
       <c r="K187" s="2" t="inlineStr"/>
       <c r="L187" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10014,12 +10014,12 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>11:-10-0</t>
+          <t>Ho:11:-10-0</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -10049,7 +10049,7 @@
       <c r="K188" s="2" t="inlineStr"/>
       <c r="L188" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10066,12 +10066,12 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>11:-20--10</t>
+          <t>Ho:11:-20--10</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -10101,7 +10101,7 @@
       <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10118,12 +10118,12 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>11:-30--20</t>
+          <t>Ho:11:-30--20</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -10153,7 +10153,7 @@
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10170,12 +10170,12 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>11:-40--30</t>
+          <t>Ho:11:-40--30</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -10205,7 +10205,7 @@
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10222,12 +10222,12 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>11:-50--40</t>
+          <t>Ho:11:-50--40</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -10257,7 +10257,7 @@
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10274,12 +10274,12 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>11:-60--50</t>
+          <t>Ho:11:-60--50</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -10309,7 +10309,7 @@
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10326,12 +10326,12 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>11:-70--60</t>
+          <t>Ho:11:-70--60</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -10361,7 +10361,7 @@
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10378,12 +10378,12 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>11:-80--70</t>
+          <t>Ho:11:-80--70</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -10413,7 +10413,7 @@
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10430,12 +10430,12 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>11:-90--80</t>
+          <t>Ho:11:-90--80</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -10465,7 +10465,7 @@
       <c r="K196" s="2" t="inlineStr"/>
       <c r="L196" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10482,12 +10482,12 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>11:-100--90</t>
+          <t>Ho:11:-100--90</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -10517,7 +10517,7 @@
       <c r="K197" s="2" t="inlineStr"/>
       <c r="L197" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10534,12 +10534,12 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>11:-125--100</t>
+          <t>Ho:11:-125--100</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -10569,7 +10569,7 @@
       <c r="K198" s="2" t="inlineStr"/>
       <c r="L198" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10586,12 +10586,12 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>11:-150--125</t>
+          <t>Ho:11:-150--125</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -10621,7 +10621,7 @@
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10638,12 +10638,12 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>11:-175--150</t>
+          <t>Ho:11:-175--150</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -10673,7 +10673,7 @@
       <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10690,12 +10690,12 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>11:-200--175</t>
+          <t>Ho:11:-200--175</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -10725,7 +10725,7 @@
       <c r="K201" s="2" t="inlineStr"/>
       <c r="L201" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10742,12 +10742,12 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>11:-250--200</t>
+          <t>Ho:11:-250--200</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -10777,7 +10777,7 @@
       <c r="K202" s="2" t="inlineStr"/>
       <c r="L202" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10794,12 +10794,12 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>13:20-25</t>
+          <t>Hu:13:20-25</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -10829,7 +10829,7 @@
       <c r="K203" s="2" t="inlineStr"/>
       <c r="L203" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10846,12 +10846,12 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>13:10-20</t>
+          <t>Hu:13:10-20</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -10881,7 +10881,7 @@
       <c r="K204" s="2" t="inlineStr"/>
       <c r="L204" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10898,12 +10898,12 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>13:0-10</t>
+          <t>Hu:13:0-10</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -10933,7 +10933,7 @@
       <c r="K205" s="2" t="inlineStr"/>
       <c r="L205" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10950,12 +10950,12 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>13:-10-0</t>
+          <t>Hu:13:-10-0</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -10985,7 +10985,7 @@
       <c r="K206" s="2" t="inlineStr"/>
       <c r="L206" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11002,12 +11002,12 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>13:-10-0</t>
+          <t>Ho:13:-10-0</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
@@ -11037,7 +11037,7 @@
       <c r="K207" s="2" t="inlineStr"/>
       <c r="L207" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11054,12 +11054,12 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>13:-20--10</t>
+          <t>Ho:13:-20--10</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -11089,7 +11089,7 @@
       <c r="K208" s="2" t="inlineStr"/>
       <c r="L208" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11106,12 +11106,12 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>13:-30--20</t>
+          <t>Ho:13:-30--20</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -11141,7 +11141,7 @@
       <c r="K209" s="2" t="inlineStr"/>
       <c r="L209" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>13:-40--30</t>
+          <t>Ho:13:-40--30</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -11193,7 +11193,7 @@
       <c r="K210" s="2" t="inlineStr"/>
       <c r="L210" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11210,12 +11210,12 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>13:-50--40</t>
+          <t>Ho:13:-50--40</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -11245,7 +11245,7 @@
       <c r="K211" s="2" t="inlineStr"/>
       <c r="L211" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11262,12 +11262,12 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>13:-60--50</t>
+          <t>Ho:13:-60--50</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -11297,7 +11297,7 @@
       <c r="K212" s="2" t="inlineStr"/>
       <c r="L212" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11314,12 +11314,12 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>13:-70--60</t>
+          <t>Ho:13:-70--60</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
@@ -11349,7 +11349,7 @@
       <c r="K213" s="2" t="inlineStr"/>
       <c r="L213" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11366,12 +11366,12 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>13:-80--70</t>
+          <t>Ho:13:-80--70</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -11401,7 +11401,7 @@
       <c r="K214" s="2" t="inlineStr"/>
       <c r="L214" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11418,12 +11418,12 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>13:-90--80</t>
+          <t>Ho:13:-90--80</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       <c r="K215" s="2" t="inlineStr"/>
       <c r="L215" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11470,12 +11470,12 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>13:-100--90</t>
+          <t>Ho:13:-100--90</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
@@ -11505,7 +11505,7 @@
       <c r="K216" s="2" t="inlineStr"/>
       <c r="L216" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11522,12 +11522,12 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>13:-125--100</t>
+          <t>Ho:13:-125--100</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
       <c r="K217" s="2" t="inlineStr"/>
       <c r="L217" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11574,12 +11574,12 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>13:-150--125</t>
+          <t>Ho:13:-150--125</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -11609,7 +11609,7 @@
       <c r="K218" s="2" t="inlineStr"/>
       <c r="L218" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11626,12 +11626,12 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>13:-175--150</t>
+          <t>Ho:13:-175--150</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
@@ -11661,7 +11661,7 @@
       <c r="K219" s="2" t="inlineStr"/>
       <c r="L219" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11678,12 +11678,12 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>13:-200--175</t>
+          <t>Ho:13:-200--175</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -11713,7 +11713,7 @@
       <c r="K220" s="2" t="inlineStr"/>
       <c r="L220" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11730,12 +11730,12 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>13:-250--200</t>
+          <t>Ho:13:-250--200</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
@@ -11765,7 +11765,7 @@
       <c r="K221" s="2" t="inlineStr"/>
       <c r="L221" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11782,12 +11782,12 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>13:-270--250</t>
+          <t>Ho:13:-270--250</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -11817,7 +11817,7 @@
       <c r="K222" s="2" t="inlineStr"/>
       <c r="L222" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11834,12 +11834,12 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>13:-300--270</t>
+          <t>Ho:13:-300--270</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -11869,7 +11869,7 @@
       <c r="K223" s="2" t="inlineStr"/>
       <c r="L223" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11886,12 +11886,12 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>14:0-10</t>
+          <t>Hu:14:0-10</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -11921,7 +11921,7 @@
       <c r="K224" s="2" t="inlineStr"/>
       <c r="L224" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11938,12 +11938,12 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>14:-10-0</t>
+          <t>Ho:14:-10-0</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
@@ -11973,7 +11973,7 @@
       <c r="K225" s="2" t="inlineStr"/>
       <c r="L225" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11990,12 +11990,12 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>14:-20--10</t>
+          <t>Ho:14:-20--10</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -12025,7 +12025,7 @@
       <c r="K226" s="2" t="inlineStr"/>
       <c r="L226" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12042,12 +12042,12 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>14:-30--20</t>
+          <t>Ho:14:-30--20</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
@@ -12077,7 +12077,7 @@
       <c r="K227" s="2" t="inlineStr"/>
       <c r="L227" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12094,12 +12094,12 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>14:-40--30</t>
+          <t>Ho:14:-40--30</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       <c r="K228" s="2" t="inlineStr"/>
       <c r="L228" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12146,12 +12146,12 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>14:-50--40</t>
+          <t>Ho:14:-50--40</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -12181,7 +12181,7 @@
       <c r="K229" s="2" t="inlineStr"/>
       <c r="L229" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12198,12 +12198,12 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>14:-60--50</t>
+          <t>Ho:14:-60--50</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -12233,7 +12233,7 @@
       <c r="K230" s="2" t="inlineStr"/>
       <c r="L230" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12250,12 +12250,12 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>14:-70--60</t>
+          <t>Ho:14:-70--60</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -12285,7 +12285,7 @@
       <c r="K231" s="2" t="inlineStr"/>
       <c r="L231" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12302,12 +12302,12 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>14:-80--70</t>
+          <t>Ho:14:-80--70</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -12337,7 +12337,7 @@
       <c r="K232" s="2" t="inlineStr"/>
       <c r="L232" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12354,12 +12354,12 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>14:-90--80</t>
+          <t>Ho:14:-90--80</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -12389,7 +12389,7 @@
       <c r="K233" s="2" t="inlineStr"/>
       <c r="L233" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12406,12 +12406,12 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>14:-100--90</t>
+          <t>Ho:14:-100--90</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -12441,7 +12441,7 @@
       <c r="K234" s="2" t="inlineStr"/>
       <c r="L234" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12458,12 +12458,12 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>14:-125--100</t>
+          <t>Ho:14:-125--100</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
@@ -12493,7 +12493,7 @@
       <c r="K235" s="2" t="inlineStr"/>
       <c r="L235" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12510,12 +12510,12 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>14:-150--125</t>
+          <t>Ho:14:-150--125</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -12545,7 +12545,7 @@
       <c r="K236" s="2" t="inlineStr"/>
       <c r="L236" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12562,12 +12562,12 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>14:-175--150</t>
+          <t>Ho:14:-175--150</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
@@ -12597,7 +12597,7 @@
       <c r="K237" s="2" t="inlineStr"/>
       <c r="L237" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12614,12 +12614,12 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>14:-200--175</t>
+          <t>Ho:14:-200--175</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -12649,7 +12649,7 @@
       <c r="K238" s="2" t="inlineStr"/>
       <c r="L238" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12666,12 +12666,12 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>14:-215--200</t>
+          <t>Ho:14:-215--200</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
@@ -12701,7 +12701,7 @@
       <c r="K239" s="2" t="inlineStr"/>
       <c r="L239" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>14:-220--215</t>
+          <t>Ho:14:-220--215</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -12753,7 +12753,7 @@
       <c r="K240" s="2" t="inlineStr"/>
       <c r="L240" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12770,12 +12770,12 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>15:20-24</t>
+          <t>Hu:15:20-24</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
@@ -12805,7 +12805,7 @@
       <c r="K241" s="2" t="inlineStr"/>
       <c r="L241" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12822,12 +12822,12 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>15:10-20</t>
+          <t>Hu:15:10-20</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
@@ -12857,7 +12857,7 @@
       <c r="K242" s="2" t="inlineStr"/>
       <c r="L242" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12874,12 +12874,12 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>15:0-10</t>
+          <t>Hu:15:0-10</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -12909,7 +12909,7 @@
       <c r="K243" s="2" t="inlineStr"/>
       <c r="L243" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12926,12 +12926,12 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>15:-10-0</t>
+          <t>Hu:15:-10-0</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
@@ -12961,7 +12961,7 @@
       <c r="K244" s="2" t="inlineStr"/>
       <c r="L244" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12978,12 +12978,12 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>15:-10-0</t>
+          <t>Ho:15:-10-0</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
@@ -13013,7 +13013,7 @@
       <c r="K245" s="2" t="inlineStr"/>
       <c r="L245" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13030,12 +13030,12 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>15:-20--10</t>
+          <t>Ho:15:-20--10</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
@@ -13065,7 +13065,7 @@
       <c r="K246" s="2" t="inlineStr"/>
       <c r="L246" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13082,12 +13082,12 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>15:-30--20</t>
+          <t>Ho:15:-30--20</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
@@ -13117,7 +13117,7 @@
       <c r="K247" s="2" t="inlineStr"/>
       <c r="L247" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13134,12 +13134,12 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>15:-40--30</t>
+          <t>Ho:15:-40--30</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
@@ -13169,7 +13169,7 @@
       <c r="K248" s="2" t="inlineStr"/>
       <c r="L248" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13186,12 +13186,12 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>15:-50--40</t>
+          <t>Ho:15:-50--40</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
@@ -13221,7 +13221,7 @@
       <c r="K249" s="2" t="inlineStr"/>
       <c r="L249" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13238,12 +13238,12 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>15:-60--50</t>
+          <t>Ho:15:-60--50</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -13273,7 +13273,7 @@
       <c r="K250" s="2" t="inlineStr"/>
       <c r="L250" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13290,12 +13290,12 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>15:-70--60</t>
+          <t>Ho:15:-70--60</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
@@ -13325,7 +13325,7 @@
       <c r="K251" s="2" t="inlineStr"/>
       <c r="L251" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13342,12 +13342,12 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>15:-80--70</t>
+          <t>Ho:15:-80--70</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
@@ -13377,7 +13377,7 @@
       <c r="K252" s="2" t="inlineStr"/>
       <c r="L252" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13394,12 +13394,12 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>15:-90--80</t>
+          <t>Ho:15:-90--80</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
@@ -13429,7 +13429,7 @@
       <c r="K253" s="2" t="inlineStr"/>
       <c r="L253" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>15:-100--90</t>
+          <t>Ho:15:-100--90</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
@@ -13481,7 +13481,7 @@
       <c r="K254" s="2" t="inlineStr"/>
       <c r="L254" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13498,12 +13498,12 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>15:-125--100</t>
+          <t>Ho:15:-125--100</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
@@ -13533,7 +13533,7 @@
       <c r="K255" s="2" t="inlineStr"/>
       <c r="L255" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13550,12 +13550,12 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>15:-150--125</t>
+          <t>Ho:15:-150--125</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
@@ -13585,7 +13585,7 @@
       <c r="K256" s="2" t="inlineStr"/>
       <c r="L256" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13602,12 +13602,12 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>16:20-29</t>
+          <t>Hu:16:20-29</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
@@ -13637,7 +13637,7 @@
       <c r="K257" s="2" t="inlineStr"/>
       <c r="L257" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13654,12 +13654,12 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>16:10-20</t>
+          <t>Hu:16:10-20</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
@@ -13689,7 +13689,7 @@
       <c r="K258" s="2" t="inlineStr"/>
       <c r="L258" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13706,12 +13706,12 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>16:0-10</t>
+          <t>Hu:16:0-10</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
@@ -13741,7 +13741,7 @@
       <c r="K259" s="2" t="inlineStr"/>
       <c r="L259" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13758,12 +13758,12 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>16:-10-0</t>
+          <t>Hu:16:-10-0</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
@@ -13793,7 +13793,7 @@
       <c r="K260" s="2" t="inlineStr"/>
       <c r="L260" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13810,12 +13810,12 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>16:-10-0</t>
+          <t>Ho:16:-10-0</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
@@ -13845,7 +13845,7 @@
       <c r="K261" s="2" t="inlineStr"/>
       <c r="L261" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13862,12 +13862,12 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>16:-20--10</t>
+          <t>Ho:16:-20--10</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
@@ -13897,7 +13897,7 @@
       <c r="K262" s="2" t="inlineStr"/>
       <c r="L262" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13914,12 +13914,12 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>16:-30--20</t>
+          <t>Ho:16:-30--20</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
@@ -13949,7 +13949,7 @@
       <c r="K263" s="2" t="inlineStr"/>
       <c r="L263" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13966,12 +13966,12 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>16:-40--30</t>
+          <t>Ho:16:-40--30</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
@@ -14001,7 +14001,7 @@
       <c r="K264" s="2" t="inlineStr"/>
       <c r="L264" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14018,12 +14018,12 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>16:-50--40</t>
+          <t>Ho:16:-50--40</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
@@ -14053,7 +14053,7 @@
       <c r="K265" s="2" t="inlineStr"/>
       <c r="L265" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14070,12 +14070,12 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>16:-60--50</t>
+          <t>Ho:16:-60--50</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
@@ -14105,7 +14105,7 @@
       <c r="K266" s="2" t="inlineStr"/>
       <c r="L266" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14122,12 +14122,12 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>16:-70--60</t>
+          <t>Ho:16:-70--60</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
@@ -14157,7 +14157,7 @@
       <c r="K267" s="2" t="inlineStr"/>
       <c r="L267" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14174,12 +14174,12 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>16:-80--70</t>
+          <t>Ho:16:-80--70</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
@@ -14209,7 +14209,7 @@
       <c r="K268" s="2" t="inlineStr"/>
       <c r="L268" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14226,12 +14226,12 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>16:-90--80</t>
+          <t>Ho:16:-90--80</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
@@ -14261,7 +14261,7 @@
       <c r="K269" s="2" t="inlineStr"/>
       <c r="L269" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14278,12 +14278,12 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>16:-100--90</t>
+          <t>Ho:16:-100--90</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
@@ -14313,7 +14313,7 @@
       <c r="K270" s="2" t="inlineStr"/>
       <c r="L270" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14330,12 +14330,12 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>16:-125--100</t>
+          <t>Ho:16:-125--100</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
@@ -14365,7 +14365,7 @@
       <c r="K271" s="2" t="inlineStr"/>
       <c r="L271" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14382,12 +14382,12 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>16:-150--125</t>
+          <t>Ho:16:-150--125</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
@@ -14417,7 +14417,7 @@
       <c r="K272" s="2" t="inlineStr"/>
       <c r="L272" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14434,12 +14434,12 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>16:-175--150</t>
+          <t>Ho:16:-175--150</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
@@ -14469,7 +14469,7 @@
       <c r="K273" s="2" t="inlineStr"/>
       <c r="L273" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14486,12 +14486,12 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>16:-200--175</t>
+          <t>Ho:16:-200--175</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
@@ -14521,7 +14521,7 @@
       <c r="K274" s="2" t="inlineStr"/>
       <c r="L274" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14538,12 +14538,12 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>16:-250--200</t>
+          <t>Ho:16:-250--200</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
@@ -14573,7 +14573,7 @@
       <c r="K275" s="2" t="inlineStr"/>
       <c r="L275" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14590,12 +14590,12 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>17:20-25</t>
+          <t>Hu:17:20-25</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
@@ -14625,7 +14625,7 @@
       <c r="K276" s="2" t="inlineStr"/>
       <c r="L276" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14642,12 +14642,12 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>17:10-20</t>
+          <t>Hu:17:10-20</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
@@ -14677,7 +14677,7 @@
       <c r="K277" s="2" t="inlineStr"/>
       <c r="L277" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14694,12 +14694,12 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>17:0-10</t>
+          <t>Hu:17:0-10</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
@@ -14729,7 +14729,7 @@
       <c r="K278" s="2" t="inlineStr"/>
       <c r="L278" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14746,12 +14746,12 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>17:-10-0</t>
+          <t>Hu:17:-10-0</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
@@ -14781,7 +14781,7 @@
       <c r="K279" s="2" t="inlineStr"/>
       <c r="L279" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14798,12 +14798,12 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>17:-10-0</t>
+          <t>Ho:17:-10-0</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
@@ -14833,7 +14833,7 @@
       <c r="K280" s="2" t="inlineStr"/>
       <c r="L280" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14850,12 +14850,12 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>17:-20--10</t>
+          <t>Ho:17:-20--10</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
@@ -14885,7 +14885,7 @@
       <c r="K281" s="2" t="inlineStr"/>
       <c r="L281" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14902,12 +14902,12 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>17:-30--20</t>
+          <t>Ho:17:-30--20</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
@@ -14937,7 +14937,7 @@
       <c r="K282" s="2" t="inlineStr"/>
       <c r="L282" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14954,12 +14954,12 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>17:-40--30</t>
+          <t>Ho:17:-40--30</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
@@ -14989,7 +14989,7 @@
       <c r="K283" s="2" t="inlineStr"/>
       <c r="L283" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15006,12 +15006,12 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>17:-50--40</t>
+          <t>Ho:17:-50--40</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
@@ -15041,7 +15041,7 @@
       <c r="K284" s="2" t="inlineStr"/>
       <c r="L284" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15058,12 +15058,12 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>17:-60--50</t>
+          <t>Ho:17:-60--50</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
@@ -15093,7 +15093,7 @@
       <c r="K285" s="2" t="inlineStr"/>
       <c r="L285" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>17:-70--60</t>
+          <t>Ho:17:-70--60</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
@@ -15145,7 +15145,7 @@
       <c r="K286" s="2" t="inlineStr"/>
       <c r="L286" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15162,12 +15162,12 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>17:-80--70</t>
+          <t>Ho:17:-80--70</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
@@ -15197,7 +15197,7 @@
       <c r="K287" s="2" t="inlineStr"/>
       <c r="L287" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15214,12 +15214,12 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>17:-90--80</t>
+          <t>Ho:17:-90--80</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
@@ -15249,7 +15249,7 @@
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15266,12 +15266,12 @@
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>17:-100--90</t>
+          <t>Ho:17:-100--90</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
@@ -15301,7 +15301,7 @@
       <c r="K289" s="2" t="inlineStr"/>
       <c r="L289" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15318,12 +15318,12 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>17:-125--100</t>
+          <t>Ho:17:-125--100</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
@@ -15353,7 +15353,7 @@
       <c r="K290" s="2" t="inlineStr"/>
       <c r="L290" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15370,12 +15370,12 @@
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>17:-150--125</t>
+          <t>Ho:17:-150--125</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
@@ -15405,7 +15405,7 @@
       <c r="K291" s="2" t="inlineStr"/>
       <c r="L291" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15422,12 +15422,12 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>17:-175--150</t>
+          <t>Ho:17:-175--150</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
@@ -15457,7 +15457,7 @@
       <c r="K292" s="2" t="inlineStr"/>
       <c r="L292" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15474,12 +15474,12 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>17:-200--175</t>
+          <t>Ho:17:-200--175</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
@@ -15509,7 +15509,7 @@
       <c r="K293" s="2" t="inlineStr"/>
       <c r="L293" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15526,12 +15526,12 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>17:-239--200</t>
+          <t>Ho:17:-239--200</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
@@ -15561,7 +15561,7 @@
       <c r="K294" s="2" t="inlineStr"/>
       <c r="L294" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15578,12 +15578,12 @@
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>19:10-20</t>
+          <t>Hu:19:10-20</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
@@ -15613,7 +15613,7 @@
       <c r="K295" s="2" t="inlineStr"/>
       <c r="L295" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15630,12 +15630,12 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>19:0-10</t>
+          <t>Hu:19:0-10</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
@@ -15665,7 +15665,7 @@
       <c r="K296" s="2" t="inlineStr"/>
       <c r="L296" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15682,12 +15682,12 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>19:-10-0</t>
+          <t>Ho:19:-10-0</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
@@ -15717,7 +15717,7 @@
       <c r="K297" s="2" t="inlineStr"/>
       <c r="L297" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15734,12 +15734,12 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>19:-20--10</t>
+          <t>Ho:19:-20--10</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
@@ -15769,7 +15769,7 @@
       <c r="K298" s="2" t="inlineStr"/>
       <c r="L298" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15786,12 +15786,12 @@
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>19:-30--20</t>
+          <t>Ho:19:-30--20</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
@@ -15821,7 +15821,7 @@
       <c r="K299" s="2" t="inlineStr"/>
       <c r="L299" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15838,12 +15838,12 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>19:-40--30</t>
+          <t>Ho:19:-40--30</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
@@ -15873,7 +15873,7 @@
       <c r="K300" s="2" t="inlineStr"/>
       <c r="L300" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15890,12 +15890,12 @@
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>19:-50--40</t>
+          <t>Ho:19:-50--40</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
@@ -15925,7 +15925,7 @@
       <c r="K301" s="2" t="inlineStr"/>
       <c r="L301" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15942,12 +15942,12 @@
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>19:-60--50</t>
+          <t>Ho:19:-60--50</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
@@ -15977,7 +15977,7 @@
       <c r="K302" s="2" t="inlineStr"/>
       <c r="L302" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15994,12 +15994,12 @@
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>19:-70--60</t>
+          <t>Ho:19:-70--60</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
@@ -16029,7 +16029,7 @@
       <c r="K303" s="2" t="inlineStr"/>
       <c r="L303" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16046,12 +16046,12 @@
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>19:-80--70</t>
+          <t>Ho:19:-80--70</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
@@ -16081,7 +16081,7 @@
       <c r="K304" s="2" t="inlineStr"/>
       <c r="L304" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16098,12 +16098,12 @@
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>19:-90--80</t>
+          <t>Ho:19:-90--80</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
@@ -16133,7 +16133,7 @@
       <c r="K305" s="2" t="inlineStr"/>
       <c r="L305" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16150,12 +16150,12 @@
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>19:-100--90</t>
+          <t>Ho:19:-100--90</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
@@ -16185,7 +16185,7 @@
       <c r="K306" s="2" t="inlineStr"/>
       <c r="L306" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16202,12 +16202,12 @@
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>19:-125--100</t>
+          <t>Ho:19:-125--100</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
@@ -16237,7 +16237,7 @@
       <c r="K307" s="2" t="inlineStr"/>
       <c r="L307" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16254,12 +16254,12 @@
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>19:-150--125</t>
+          <t>Ho:19:-150--125</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
@@ -16289,7 +16289,7 @@
       <c r="K308" s="2" t="inlineStr"/>
       <c r="L308" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16306,12 +16306,12 @@
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>19:-175--150</t>
+          <t>Ho:19:-175--150</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
@@ -16341,7 +16341,7 @@
       <c r="K309" s="2" t="inlineStr"/>
       <c r="L309" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16358,12 +16358,12 @@
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>19:-200--175</t>
+          <t>Ho:19:-200--175</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
@@ -16393,7 +16393,7 @@
       <c r="K310" s="2" t="inlineStr"/>
       <c r="L310" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16410,12 +16410,12 @@
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>19:-216--200</t>
+          <t>Ho:19:-216--200</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
@@ -16445,7 +16445,7 @@
       <c r="K311" s="2" t="inlineStr"/>
       <c r="L311" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16462,12 +16462,12 @@
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>19:-250--216</t>
+          <t>Ho:19:-250--216</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
@@ -16497,7 +16497,7 @@
       <c r="K312" s="2" t="inlineStr"/>
       <c r="L312" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16514,12 +16514,12 @@
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>20:10-19</t>
+          <t>Hu:20:10-19</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
@@ -16549,7 +16549,7 @@
       <c r="K313" s="2" t="inlineStr"/>
       <c r="L313" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16566,12 +16566,12 @@
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>20:0-10</t>
+          <t>Hu:20:0-10</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
@@ -16601,7 +16601,7 @@
       <c r="K314" s="2" t="inlineStr"/>
       <c r="L314" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16618,12 +16618,12 @@
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>20:-10-0</t>
+          <t>Hu:20:-10-0</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
@@ -16653,7 +16653,7 @@
       <c r="K315" s="2" t="inlineStr"/>
       <c r="L315" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16670,12 +16670,12 @@
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>20:-10-0</t>
+          <t>Ho:20:-10-0</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
@@ -16705,7 +16705,7 @@
       <c r="K316" s="2" t="inlineStr"/>
       <c r="L316" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16722,12 +16722,12 @@
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>20:-20--10</t>
+          <t>Ho:20:-20--10</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
@@ -16757,7 +16757,7 @@
       <c r="K317" s="2" t="inlineStr"/>
       <c r="L317" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16774,12 +16774,12 @@
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>20:-30--20</t>
+          <t>Ho:20:-30--20</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
@@ -16809,7 +16809,7 @@
       <c r="K318" s="2" t="inlineStr"/>
       <c r="L318" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16826,12 +16826,12 @@
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>20:-40--30</t>
+          <t>Ho:20:-40--30</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
@@ -16861,7 +16861,7 @@
       <c r="K319" s="2" t="inlineStr"/>
       <c r="L319" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16878,12 +16878,12 @@
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>20:-50--40</t>
+          <t>Ho:20:-50--40</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
@@ -16913,7 +16913,7 @@
       <c r="K320" s="2" t="inlineStr"/>
       <c r="L320" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16930,12 +16930,12 @@
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>20:-60--50</t>
+          <t>Ho:20:-60--50</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr">
@@ -16965,7 +16965,7 @@
       <c r="K321" s="2" t="inlineStr"/>
       <c r="L321" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16982,12 +16982,12 @@
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>20:-70--60</t>
+          <t>Ho:20:-70--60</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
@@ -17017,7 +17017,7 @@
       <c r="K322" s="2" t="inlineStr"/>
       <c r="L322" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17034,12 +17034,12 @@
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>20:-80--70</t>
+          <t>Ho:20:-80--70</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
@@ -17069,7 +17069,7 @@
       <c r="K323" s="2" t="inlineStr"/>
       <c r="L323" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17086,12 +17086,12 @@
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>20:-90--80</t>
+          <t>Ho:20:-90--80</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
@@ -17121,7 +17121,7 @@
       <c r="K324" s="2" t="inlineStr"/>
       <c r="L324" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17138,12 +17138,12 @@
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>20:-100--90</t>
+          <t>Ho:20:-100--90</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
@@ -17173,7 +17173,7 @@
       <c r="K325" s="2" t="inlineStr"/>
       <c r="L325" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17190,12 +17190,12 @@
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>20:-125--100</t>
+          <t>Ho:20:-125--100</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
@@ -17225,7 +17225,7 @@
       <c r="K326" s="2" t="inlineStr"/>
       <c r="L326" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17242,12 +17242,12 @@
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>20:-150--125</t>
+          <t>Ho:20:-150--125</t>
         </is>
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
@@ -17277,7 +17277,7 @@
       <c r="K327" s="2" t="inlineStr"/>
       <c r="L327" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17294,12 +17294,12 @@
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>20:-175--150</t>
+          <t>Ho:20:-175--150</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
@@ -17329,7 +17329,7 @@
       <c r="K328" s="2" t="inlineStr"/>
       <c r="L328" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17346,12 +17346,12 @@
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>20:-200--175</t>
+          <t>Ho:20:-200--175</t>
         </is>
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
@@ -17381,7 +17381,7 @@
       <c r="K329" s="2" t="inlineStr"/>
       <c r="L329" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17398,12 +17398,12 @@
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>20:-250--200</t>
+          <t>Ho:20:-250--200</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
@@ -17433,7 +17433,7 @@
       <c r="K330" s="2" t="inlineStr"/>
       <c r="L330" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17450,12 +17450,12 @@
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>20:-300--250</t>
+          <t>Ho:20:-300--250</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
@@ -17485,7 +17485,7 @@
       <c r="K331" s="2" t="inlineStr"/>
       <c r="L331" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17502,12 +17502,12 @@
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>21:10-20</t>
+          <t>Hu:21:10-20</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
@@ -17537,7 +17537,7 @@
       <c r="K332" s="2" t="inlineStr"/>
       <c r="L332" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17554,12 +17554,12 @@
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>21:0-10</t>
+          <t>Hu:21:0-10</t>
         </is>
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
@@ -17589,7 +17589,7 @@
       <c r="K333" s="2" t="inlineStr"/>
       <c r="L333" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17606,12 +17606,12 @@
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>21:-10-0</t>
+          <t>Ho:21:-10-0</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
@@ -17641,7 +17641,7 @@
       <c r="K334" s="2" t="inlineStr"/>
       <c r="L334" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17658,12 +17658,12 @@
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>21:-20--10</t>
+          <t>Ho:21:-20--10</t>
         </is>
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
@@ -17693,7 +17693,7 @@
       <c r="K335" s="2" t="inlineStr"/>
       <c r="L335" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17710,12 +17710,12 @@
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>21:-30--20</t>
+          <t>Ho:21:-30--20</t>
         </is>
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
@@ -17745,7 +17745,7 @@
       <c r="K336" s="2" t="inlineStr"/>
       <c r="L336" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17762,12 +17762,12 @@
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>21:-40--30</t>
+          <t>Ho:21:-40--30</t>
         </is>
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
@@ -17797,7 +17797,7 @@
       <c r="K337" s="2" t="inlineStr"/>
       <c r="L337" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17814,12 +17814,12 @@
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>21:-50--40</t>
+          <t>Ho:21:-50--40</t>
         </is>
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr">
@@ -17849,7 +17849,7 @@
       <c r="K338" s="2" t="inlineStr"/>
       <c r="L338" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17866,12 +17866,12 @@
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>21:-60--50</t>
+          <t>Ho:21:-60--50</t>
         </is>
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E339" s="2" t="inlineStr">
@@ -17901,7 +17901,7 @@
       <c r="K339" s="2" t="inlineStr"/>
       <c r="L339" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17918,12 +17918,12 @@
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>21:-70--60</t>
+          <t>Ho:21:-70--60</t>
         </is>
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr">
@@ -17953,7 +17953,7 @@
       <c r="K340" s="2" t="inlineStr"/>
       <c r="L340" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -17970,12 +17970,12 @@
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>21:-80--70</t>
+          <t>Ho:21:-80--70</t>
         </is>
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E341" s="2" t="inlineStr">
@@ -18005,7 +18005,7 @@
       <c r="K341" s="2" t="inlineStr"/>
       <c r="L341" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18022,12 +18022,12 @@
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>21:-90--80</t>
+          <t>Ho:21:-90--80</t>
         </is>
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr">
@@ -18057,7 +18057,7 @@
       <c r="K342" s="2" t="inlineStr"/>
       <c r="L342" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18074,12 +18074,12 @@
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>21:-100--90</t>
+          <t>Ho:21:-100--90</t>
         </is>
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E343" s="2" t="inlineStr">
@@ -18109,7 +18109,7 @@
       <c r="K343" s="2" t="inlineStr"/>
       <c r="L343" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18126,12 +18126,12 @@
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>21:-125--100</t>
+          <t>Ho:21:-125--100</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
@@ -18161,7 +18161,7 @@
       <c r="K344" s="2" t="inlineStr"/>
       <c r="L344" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18178,12 +18178,12 @@
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>21:-150--125</t>
+          <t>Ho:21:-150--125</t>
         </is>
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr">
@@ -18213,7 +18213,7 @@
       <c r="K345" s="2" t="inlineStr"/>
       <c r="L345" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18230,12 +18230,12 @@
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>21:-175--150</t>
+          <t>Ho:21:-175--150</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr">
@@ -18265,7 +18265,7 @@
       <c r="K346" s="2" t="inlineStr"/>
       <c r="L346" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18282,12 +18282,12 @@
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>21:-200--175</t>
+          <t>Ho:21:-200--175</t>
         </is>
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr">
@@ -18317,7 +18317,7 @@
       <c r="K347" s="2" t="inlineStr"/>
       <c r="L347" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18334,12 +18334,12 @@
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>21:-250--200</t>
+          <t>Ho:21:-250--200</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
@@ -18369,7 +18369,7 @@
       <c r="K348" s="2" t="inlineStr"/>
       <c r="L348" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Mn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
